--- a/AAII_Financials/Quarterly/NFLX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NFLX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
   <si>
     <t>NFLX</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12559900</v>
+      </c>
+      <c r="E8" s="3">
         <v>12249800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12050800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11510300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11079200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10542800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10246500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9824700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9559300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9370400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8832800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8541700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8187300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8161500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7852100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7925600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7970100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7867800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7709300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7483500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7341800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7163300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6644400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6435600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6148300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5767700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5467400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5244900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4923100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4521000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4186800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3999400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3907300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3700900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3285800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2984900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2785500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2636600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2477500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2290200</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6037000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5888200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6522600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6164300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5325300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5263100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5767400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5119900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5174100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4977100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5307500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4930800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4673500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4803600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5404200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4788700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4690800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4284700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5239600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4206600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4018000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3868500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3894200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3590800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3442700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3381700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3466000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3097900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3005700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2870600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3069300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2412300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2289900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2196100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2107400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1993000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1902300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1657000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1654400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1532800</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6523000</v>
+      </c>
+      <c r="E10" s="3">
         <v>6361500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5528100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5346100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5753900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5279700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4479100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4704800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4385200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4393400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3525300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3610900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3513800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3357900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2447900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3136900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3279300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3583100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2469700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3276900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3323800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3294800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2750200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2844800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2705600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2386000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2001400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2147000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1917400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1650400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1117600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1587100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1617400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1504800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1178400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>991900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>883200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>979600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>823100</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>757400</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,130 +1248,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1007700</v>
+      </c>
+      <c r="E12" s="3">
         <v>959700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>890300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>853600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>824700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>822800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>776500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>735100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>711300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>702500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>673300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>657200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>658000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>687300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>673900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>662700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>716800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>657500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>647500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>563900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>537300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>525200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>486900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>453800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>435000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>453800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>409400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>379800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>383200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>372800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>276800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>327000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>317200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>300700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>273400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>255200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>267100</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>257100</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>225200</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>216100</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,16 +1496,19 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2800000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>24</v>
@@ -1523,14 +1543,14 @@
       <c r="P14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>24</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>24</v>
@@ -1547,20 +1567,20 @@
       <c r="X14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z14" s="3">
         <v>271000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>277000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>201000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>218000</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>24</v>
@@ -1577,8 +1597,8 @@
       <c r="AH14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
@@ -1601,53 +1621,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>100500</v>
+      </c>
+      <c r="E15" s="3">
         <v>98600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>86000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>87300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>80000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>80100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>79500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>80900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>81200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>87200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>86600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>90700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>89400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>90300</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>8367300</v>
+      </c>
+      <c r="E17" s="3">
         <v>8292800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9094100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8262100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7304500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7195800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7973700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6915200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6956500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6737900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7336700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6625300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6360100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6447200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7302100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6392600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6391900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5896100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7077500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5728200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5494100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5203400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5690200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5120800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4790400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4809400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5008900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4264700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4216700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4061900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3971100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3518700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3445100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3254300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3040500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2776200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2657700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2379700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2323600</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2184200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>4192600</v>
+      </c>
+      <c r="E18" s="3">
         <v>3957000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2956700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3248200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3774700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3347000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2272800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2909500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2602800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2632500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1496100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1916400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1827200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1714300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>550000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1533000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1578200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1971700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>631800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1755300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1847700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1959900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>954200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1314800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1357900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>958300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>458500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>980200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>706400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>459100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>215700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>480700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>462200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>446600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>245300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>208700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>127800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>256900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>153900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>106000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E20" s="3">
         <v>17800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>28500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>30500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>32400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>31100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>33900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>97700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-16000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-88400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>288800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-89000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>23000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>107000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-340000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>261400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>220300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>195600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>108500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>96100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-62500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>269100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-250600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-256300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-133200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>21700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-131300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>192700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-53500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>76100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>32500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>7000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>68000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-65800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-38700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-31700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-58400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>13600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>4262800</v>
+      </c>
+      <c r="E21" s="3">
         <v>4037700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3014100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3305000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3822300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3396000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2318400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2892700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2700100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2808100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1293900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2096100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1893600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1697700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4248200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5533200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5143400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5408200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4545600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4884700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4630300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4983900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3718200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3820900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3858600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3491900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2911800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3486300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2918000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2691900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2334000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2430600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2378900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2159900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1951800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1836900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1655300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1609900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1497800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1372500</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>175700</v>
+      </c>
+      <c r="E22" s="3">
         <v>262100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>234400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>175300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>182600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>184200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>192600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>184800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>168000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>173300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>175200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>175600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>174800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>174200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>170600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>172600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>175500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>187600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>189400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>190400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>191300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>194400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>197200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>197100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>189200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>184100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>177800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>160700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>152000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>135500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>128800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>108900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>101600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>81200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>75300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>60700</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>55500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>46700</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>43600</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>35500</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>4068600</v>
+      </c>
+      <c r="E23" s="3">
         <v>6547100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2767700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3109400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3631700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3213700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2134300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2703000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2513900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2614600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1148200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1909000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1679300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1468900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>39300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1621800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1623100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1979700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>550900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1661000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1593800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2034500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>506400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>861500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1035600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>795900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>149300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1012300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>500900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>399700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>119400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>378800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>428600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>299600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>131300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>116200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>14000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>223800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>90300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>79100</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>667200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1264300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>349200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>562500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>506300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>323400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>265700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>339400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>366600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>282400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>210300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>231600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>191700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>163800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>353000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>223600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>182100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>382200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>198200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>211900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>240800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>327800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>51500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>71500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>315400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>86800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-310100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>347100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>230300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>55600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-23200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>13600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>44300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>9500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-133300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-13400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-51600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>45600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>23500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>27600</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>3401400</v>
+      </c>
+      <c r="E26" s="3">
         <v>5282800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2418500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2546900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3125400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2890400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1868600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2363500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2147300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2332200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>937800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1677400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1487600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1305100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-313700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1398200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1441000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1597400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>352700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1449100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1353000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1706700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>455000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>790000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>720200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>709100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>459400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>665200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>270700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>344100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>142600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>365200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>384300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>290100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>264600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>129600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>65600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>178200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>66700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>3401400</v>
+      </c>
+      <c r="E27" s="3">
         <v>5282800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2418500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2546900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3125400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2890400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1868600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2363500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2147300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2332200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>937800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1677400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1487600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1305100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-313700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1398200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1441000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1597400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>352700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1449100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1353000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1706700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>455000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>790000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>720200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>709100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>459400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>665200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>270700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>344100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>142600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>365200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>384300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>290100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>264600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>129600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>65600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>178200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>66700</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3195,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>369000</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>24</v>
@@ -3206,11 +3267,11 @@
       <c r="T29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V29" s="3">
         <v>254800</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>24</v>
@@ -3218,11 +3279,11 @@
       <c r="X29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z29" s="3">
         <v>87200</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>24</v>
@@ -3230,11 +3291,11 @@
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD29" s="3">
         <v>127500</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -3242,23 +3303,23 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-8700</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>37600</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-79100</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-17800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-28500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-30500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-32400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-31100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-33900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-97700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>16000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>88400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-288800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>89000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-23000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-107000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>340000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-261400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-220300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-195600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-108500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-96100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>62500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-269100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>250600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>256300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>133200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-21700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>131300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-192700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>53500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-76100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-32500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-68000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>65800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>38700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>31700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>58400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-13600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>20000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-8600</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3401400</v>
+      </c>
+      <c r="E33" s="3">
         <v>5282800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2418500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2546900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3125400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2890400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1868600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2363500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2147300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2332200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>937800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1677400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1487600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1305100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>55300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1398200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1441000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1597400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>607400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1449100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1353000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1706700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>542200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>790000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>720200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>709100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>587000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>665200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>270700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>344100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>133900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>402800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>384300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>290100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>185500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>129600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>65600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>178200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>66700</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3401400</v>
+      </c>
+      <c r="E35" s="3">
         <v>5282800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2418500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2546900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3125400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2890400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1868600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2363500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2147300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2332200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>937800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1677400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1487600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1305100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>55300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1398200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1441000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1597400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>607400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1449100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1353000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1706700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>542200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>790000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>720200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>709100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>587000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>665200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>270700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>344100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>133900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>402800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>384300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>290100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>185500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>129600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>65600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>178200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>66700</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9099200</v>
+      </c>
+      <c r="E41" s="3">
         <v>12259800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9033700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9287300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8177400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7199800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7804700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7457000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6624900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7024800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7116900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7353200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7662800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6714600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5147200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6113700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5819400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6008900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6027800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7526700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7777500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8403700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8205600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>8392400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7153200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5151900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5018400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4435000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5004200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3348600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3794500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3067500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3906400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2593700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2822800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1746500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1918800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1077800</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1467600</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>969200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4353,43 +4443,43 @@
         <v>28700</v>
       </c>
       <c r="F42" s="3">
+        <v>28700</v>
+      </c>
+      <c r="G42" s="3">
         <v>37100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>213100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1171100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1779000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1766900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>31000</v>
-      </c>
-      <c r="L42" s="3">
-        <v>21000</v>
       </c>
       <c r="M42" s="3">
         <v>21000</v>
       </c>
       <c r="N42" s="3">
+        <v>21000</v>
+      </c>
+      <c r="O42" s="3">
         <v>514200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>914200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1112900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>911300</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>24</v>
@@ -4406,8 +4496,8 @@
       <c r="W42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -4442,151 +4532,157 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
-      <c r="AJ42" s="3" t="s">
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK42" s="3">
-        <v>0</v>
-      </c>
       <c r="AL42" s="3">
         <v>0</v>
       </c>
       <c r="AM42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="3">
         <v>246100</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>263400</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>266200</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>374100</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2004000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2003700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2583500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1688800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1579900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1448000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1988300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1217700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1276400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1228700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1842100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1140000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1218300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1025500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>988900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>875000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>765400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>824700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>804300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>782400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>775200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>807000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>610800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1224900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1206100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1081500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>979100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>466200</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
-      </c>
       <c r="AF43" s="3">
         <v>0</v>
       </c>
       <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
         <v>5151200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4987900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4803700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4626500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4310900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>4223400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>4149100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>4026600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3726300</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3632400</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,257 +4803,266 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2136900</v>
+      </c>
+      <c r="E45" s="3">
         <v>2177000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>876300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1482200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1571700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1394300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1096400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1251800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1237700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1192700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>529300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1287700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1229500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1143600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2219100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1828100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1255900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1264400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1237700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1106800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1051500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>896800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>945200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>209200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>204800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>214400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>181000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>426600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>872900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>820400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>748500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>674500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>636900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>597400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>536200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>415500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>386800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>292500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>260200</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>218200</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13853300</v>
+      </c>
+      <c r="E46" s="3">
         <v>17071000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13020200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12962900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11993100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11697600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13100400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12129100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9615600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9921300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9918100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10779500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11506300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10482600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9266500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8816900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7840800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8098000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8069800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9415800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9604300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10107500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9761600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9826500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8564100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6447800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6178500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5327800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5877200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4168900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>9694100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8730000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>9346900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7817600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7670000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>6385300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>6700800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>5660300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>5720300</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>5193900</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>24</v>
+      <c r="D47" s="3">
+        <v>1100</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>24</v>
@@ -4995,8 +5100,8 @@
       <c r="P47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5073,252 +5178,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4436400</v>
+      </c>
+      <c r="E48" s="3">
         <v>4248300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4211500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4134600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3918900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3739600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3696100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3782700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3734200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3660500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3568300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3622900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3659700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3588100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3625400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3584300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3703300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3867500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3770000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3469600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3210100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3023100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2997900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2767100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2563900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2152500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2097200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1513000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1460400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1246400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>471700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>371200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>349600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>341900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>319400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>322400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>309800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>275100</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>250400</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>191900</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12229700</v>
+      </c>
+      <c r="E49" s="3">
         <v>12268100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12138600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12182200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12273100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12393100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12422300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12307700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12358500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12549500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12722700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12459400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12622400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12533400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>32736700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>32777300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>32533200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>31191900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>30919500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>28974000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>27291600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>26044000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>25384000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>25067600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>25155100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>25266900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>24504600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>23235000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>21945700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>20888800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>14951100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>13408400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>12292100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>11314800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>10371100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>9739700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>9078500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>8029100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>7274500</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>6677700</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27929900</v>
+      </c>
+      <c r="E52" s="3">
         <v>27428500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>24164600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25655100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24914600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>24257300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>23121500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24062400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>23390600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>22696400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21522100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>22640000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>23029000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>22886200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2966200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2383700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2273600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2173400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1825300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>880500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>864900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>948400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1136900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>961300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>892100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1192800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1195400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>866000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>888000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>914600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>910800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>856700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>674900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>678500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>652300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>504100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>428100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>394600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>341400</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>283900</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>58450400</v>
+      </c>
+      <c r="E54" s="3">
         <v>61015900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>55597000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>54934800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>53099700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>52087600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>53630400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>52281800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>49098900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>48827700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>48732000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>49501800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>50817500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>49490300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>48594800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>47562200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>46350900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>45330900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>44584700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>42739900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>40971000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>40123000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>39280400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>38622500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>37175300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>35059900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>33975700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>30941700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>30171300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>27218600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>25974400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>23366200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>22663500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>20152800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>19012700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>16951500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>16517200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>14359100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>13586600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>12347300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,175 +6145,179 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>814600</v>
+      </c>
+      <c r="E57" s="3">
         <v>894700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>793200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>632700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>614500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>899900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>642000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>598600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>607300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>747400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>534400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>615400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>592000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5151700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4786000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4679200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4683500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5130500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4754000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4820800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4830900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5085700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5141000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5111400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5307100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5087900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5304700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5290400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5302800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5244500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5054400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4989300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4902300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4532600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4443500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>4368800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>4156300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>3945600</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>3783000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2915200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1432700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1459300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>457400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>453900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1443100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2212900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2253100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2217100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1196600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>783200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>777000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>776200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>762500</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6194,31 +6328,31 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>699800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>699500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>699100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>698800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>499900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>499500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>499200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>498800</v>
-      </c>
-      <c r="AC58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>24</v>
@@ -6235,8 +6369,8 @@
       <c r="AH58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
@@ -6259,496 +6393,511 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5996700</v>
+      </c>
+      <c r="E59" s="3">
         <v>6155800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6298600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6313000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6421300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5932100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6232400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6218400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5894100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5947900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6049500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5572300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5752300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5606900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2779300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2979900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2820800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3056200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2658700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2595800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2313000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2432100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2220200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2299300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2015900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2047800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1767800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1953200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1643600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1555000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1242800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1243800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1090300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1103300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>933700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>867100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>754200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>755000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>641100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>628400</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12134900</v>
+      </c>
+      <c r="E60" s="3">
         <v>12131600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10980900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9731900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8942300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9718500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10755400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10707100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10140000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9289200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8860700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8338700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8675800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8316100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7931000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7765900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7500000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7739700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8489000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8049200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7832900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7961800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7805800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7939800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7626400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7853700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6855700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7257900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6934000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6857800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6487300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6298200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6079600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6005600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5466300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>5310700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>5122900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>4911200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>4586700</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>4411400</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13739500</v>
+      </c>
+      <c r="E61" s="3">
         <v>15309500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15516500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16626100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16480000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15980300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15782000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16255600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14307100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15315000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>16190200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15987200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16217500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16193400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14353100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13888100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14233300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14534600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14693100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14793700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>14926900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14860600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>15809100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>15547600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>15295000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>14170700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14759300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>12425700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>12594100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10305000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10360100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8336600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>8342100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6542400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6499400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>4888800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>4836500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3365400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3364300</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2374000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2424000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2448400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2376800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2622800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2725400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2360700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2236800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2598400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2539100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2858100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2966600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3068200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3092000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3152700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5533300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5380000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5541600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5512600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5553400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4582300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4347300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4416600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4600200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4801800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4919100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4626200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4778600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4396600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4537700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4352700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3888300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3721800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3745200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3584100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3465000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3424700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3445300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3108800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2955800</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>3033000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>28298400</v>
+      </c>
+      <c r="E66" s="3">
         <v>29889500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>28981500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>28980800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>28147800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>28059600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>28886800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>29561100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26986200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27462300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28143700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27394200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>27985300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>27662100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>27817400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>27034000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>27275000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>27786900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28735400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>27425200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>27107100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>27238900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>28215100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>28289200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>27840500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>26650600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>26393600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>24080200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>24065800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>21515600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>20735600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>18356600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>18166900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>16132100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>15430800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>13624200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>13404700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>11385400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>10906800</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>9818400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>50966300</v>
+      </c>
+      <c r="E72" s="3">
         <v>47564900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>42282100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>39863600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>37316700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>34191300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>31300900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>29432300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27068800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>24921500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>22589300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21651400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19974000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18486400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17181300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17126000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15727800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14286800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12689400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>12081900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>10632900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9279900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7573100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7031000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6241000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5520800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4811700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4224800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3559500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>3288900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2942400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2808400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2405600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2021200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1731100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1545600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1416000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1350400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1128600</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1061900</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30152100</v>
+      </c>
+      <c r="E76" s="3">
         <v>31126400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26615500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25954000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>24951900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24028100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24743600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22720700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22112700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21365400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20588300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22107600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22832200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21828200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20777400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20528100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19076000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17544000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15849200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15314600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13863900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12884100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11065200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10333300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9334800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8409300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7582200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6861500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6105500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5703100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5238800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5009700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4496600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4020700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3582000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3327400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3112500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>2973700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>2679800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>2529000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3401400</v>
+      </c>
+      <c r="E81" s="3">
         <v>5282800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2418500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2546900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3125400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2890400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1868600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2363500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2147300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2332200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>937800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1677400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1487600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1305100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>55300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1398200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1441000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1597400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>607400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1449100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1353000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1706700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>542200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>790000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>720200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>709100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>587000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>665200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>270700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>344100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>133900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>402800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>384300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>290100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>185500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>129600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>65600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>178200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>66700</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E83" s="3">
         <v>80100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>79500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>80900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>81200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>87200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>86600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>90700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>89400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>90300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>93400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>85200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>83500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>74600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4038200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3738800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3344900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3241000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3805300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3033300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2845200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2754900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>3014600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2762300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2633800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2511900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2607500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2306700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2257400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2148200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2076900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1932900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1837600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1767900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1732900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1646700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1569300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1320700</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1344700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>1238500</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1743800</v>
+      </c>
+      <c r="E89" s="3">
         <v>5290200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2111600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2825200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2423300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2789200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1536900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2321100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1290800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2212500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1663000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1992300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1440200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2178700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>443900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>556800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>102800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>922800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-403300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>82400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-63800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>777300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-137700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1263800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1041100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>259900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1462000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-501800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-543800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-379800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1235100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-690400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-518200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-236800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-488000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-419600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-534500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-343900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-557200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-461900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-218600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-196100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-239300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-164700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-155900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-128300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-158700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-126900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-78300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-75700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-81600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-103900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-101000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-62000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-111600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-85000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-90000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-121200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-166000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-167300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-110300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-81000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-148400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-109800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-141700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-98000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-107700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-45300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-39600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-60400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-70100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-39300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-27300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-37200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-21600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-34000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-65200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-77900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-79800</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-44600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-218600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-781900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-256500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>43900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>768700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>485700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-158700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1869100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-78300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-75700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>411600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>296100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>97700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-263700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1586900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-85000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-158900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-245700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-954300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-188600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-111300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-85600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-146400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-118700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-142000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-98300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-207600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-49400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-50000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-80100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-80400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-168700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-40300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-49800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-35800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>202200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-56400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-75600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>24400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10266,8 +10500,8 @@
       <c r="P96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4669600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1230800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2077400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1737000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2502900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4028300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-678700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>226600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1489400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2132900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2452300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2475100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-649300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-374100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>6700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>11300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-686300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-136000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-81600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-480300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-451900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>34000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>68700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1091000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>43700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2223800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>12000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2246900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>23000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2053900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>29200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1909400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>56000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1597900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>34400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1420400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>24200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>1042500</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>287500</v>
+      </c>
+      <c r="E101" s="3">
         <v>150100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-351300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>153500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-122700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-95800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>139300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-122700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>39600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>26400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>166600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-180100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-145200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>166600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-180100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-145200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-11400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-4200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-63800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>23500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-42100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>66700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>28500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>11800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-70900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>29800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-29300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5000</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>-5000</v>
       </c>
       <c r="AG101" s="3">
         <v>-5000</v>
       </c>
       <c r="AH101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-36300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>7200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>2200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>10700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>11500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>5500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-11300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3164100</v>
+      </c>
+      <c r="E102" s="3">
         <v>3227700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-251700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1110300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>976500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-603300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>348300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>832000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-399500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-91900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-238300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-309400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>928200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1567400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-969700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>295900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-190100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-20600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1497900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-251700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-631800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>197600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-183400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1242200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2001900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>134400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>584100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-568500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1658100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-441900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>733500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-835400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1314500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-223300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1076300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-172300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>841000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-389800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>498400</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-421800</v>
       </c>
     </row>
